--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F45B0F1C-7A4A-49C0-8F72-88029ED5FC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A591CB6-2522-42AE-AD1E-562177B47CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="4294937190" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>고유 ID</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>Sprites/portraitangry</t>
+  </si>
+  <si>
+    <t>dialogue_default_endinspect</t>
+  </si>
+  <si>
+    <t>[{ObjectName}]을(를) 소지품에 추가했다.</t>
   </si>
 </sst>
 </file>
@@ -704,9 +710,13 @@
       <c r="R9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A10" s="9"/>
+      <c r="A10" s="9" t="s">
+        <v>27</v>
+      </c>
       <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
+      <c r="C10" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A591CB6-2522-42AE-AD1E-562177B47CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{459A3B21-6565-42CB-BD9F-60EA33663870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="4294937190" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
+    <sheet name="Dialogue" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="83">
   <si>
     <t>고유 ID</t>
   </si>
@@ -47,6 +47,9 @@
     <t>string[]</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -68,68 +71,236 @@
     <t>CharacterPortraitPath</t>
   </si>
   <si>
-    <t>dialogue_test_100</t>
-  </si>
-  <si>
-    <t>char_testNPC</t>
-  </si>
-  <si>
-    <t>테스트용 대화입니다.&lt;np&gt;다음 대화가 잘 나오는지 확인.&lt;np&gt;선택지로 진입합니다.</t>
-  </si>
-  <si>
-    <t>dialogue_test_200</t>
-  </si>
-  <si>
-    <t>Sprites/portraitnormal</t>
-  </si>
-  <si>
-    <t>캐릭터의 표정을 바꾸는 선택지입니다.&lt;np&gt;어떤 표정으로 바꿀까요?</t>
-  </si>
-  <si>
-    <t>기쁜 표정, 슬픈 표정, 화난 표정</t>
-  </si>
-  <si>
-    <t>dialogue_test_200_selection1, dialogue_test_200_selection2, dialogue_test_200_selection3</t>
-  </si>
-  <si>
-    <t>dialogue_test_200_selection1</t>
-  </si>
-  <si>
-    <t>캐릭터가 기쁜 표정을 지었다</t>
-  </si>
-  <si>
-    <t>Sprites/portraithappy</t>
-  </si>
-  <si>
-    <t>dialogue_test_200_selection2</t>
-  </si>
-  <si>
-    <t>캐릭터가 슬픈 표정을 지었다</t>
-  </si>
-  <si>
-    <t>Sprites/portraitsad</t>
-  </si>
-  <si>
-    <t>dialogue_test_200_selection3</t>
-  </si>
-  <si>
-    <t>캐릭터가 화난 표정을 지었다</t>
-  </si>
-  <si>
-    <t>Sprites/portraitangry</t>
+    <t>AddLikeAbility</t>
+  </si>
+  <si>
+    <t>BGMPath</t>
+  </si>
+  <si>
+    <t>OpenInspectObjectDataId</t>
+  </si>
+  <si>
+    <t>DialogueFlagId</t>
+  </si>
+  <si>
+    <t>CompleteJournalDataId</t>
+  </si>
+  <si>
+    <t>dialogue_omakegirl_start_first</t>
+  </si>
+  <si>
+    <t>char_girl</t>
+  </si>
+  <si>
+    <t>아... 안녕하세요...&lt;np&gt;처음 뵙겠습니다. 저는 윤하린이에요...</t>
+  </si>
+  <si>
+    <t>dialogue_omakegirl_100</t>
+  </si>
+  <si>
+    <t>dialogue_omakegirl_start_repeat</t>
+  </si>
+  <si>
+    <t>무슨 일이세요..?</t>
+  </si>
+  <si>
+    <t>#하린에게 무엇을 할까?</t>
+  </si>
+  <si>
+    <t>칭찬한다, 아재개그를 한다, 위협한다</t>
+  </si>
+  <si>
+    <t>dialogue_omakegirl_100_selection1, dialogue_omakegirl_100_selection2, dialogue_omakegirl_100_selection3</t>
+  </si>
+  <si>
+    <t>dialogue_omakegirl_100_selection1</t>
+  </si>
+  <si>
+    <t>가, 갑자기 무슨 말씀을 하시는 거에요?</t>
+  </si>
+  <si>
+    <t>dialogue_omakegirl_100_selection1_100</t>
+  </si>
+  <si>
+    <t>Portraits/Girl_Portrait_Embarrassed</t>
+  </si>
+  <si>
+    <t>dialogue_omakegirl_100_selection2</t>
+  </si>
+  <si>
+    <t>아, 아하하...&lt;np&gt;#부장님의 아재개그를 들은 사원 같은 표정이다.</t>
+  </si>
+  <si>
+    <t>Portraits/Girl_Portrait_NervousSmile</t>
+  </si>
+  <si>
+    <t>dialogue_omakegirl_100_selection3</t>
+  </si>
+  <si>
+    <t>히익! 살려 주세요..!&lt;np&gt;#뭔가 트라우마를 떠올린 것 같다.&lt;np&gt;#그녀의 기분이 나빠진 것 같다.</t>
+  </si>
+  <si>
+    <t>Portraits/Girl_Portrait_Scared</t>
   </si>
   <si>
     <t>dialogue_default_endinspect</t>
   </si>
   <si>
-    <t>[{ObjectName}]을(를) 소지품에 추가했다.</t>
+    <t>{ObjectName}의 정보를 조사 기록에 등록했다.</t>
+  </si>
+  <si>
+    <t>어쨌든 그, 감사해요...&lt;np&gt;#내심 그녀의 기분이 좋아진 것 같다.</t>
+  </si>
+  <si>
+    <t>Portraits/Girl_Portrait_LikeDefault</t>
+  </si>
+  <si>
+    <t>dialogue_omakepilot_start_first</t>
+  </si>
+  <si>
+    <t>char_pilot</t>
+  </si>
+  <si>
+    <t>안녕하세요. 초상화도 대충 만든 엑스트라입니다.</t>
+  </si>
+  <si>
+    <t>dialogue_omakepilot_start_repeat</t>
+  </si>
+  <si>
+    <t>...나같은 엑스트라한테 두 번 말 거는 사람은 없겠지?</t>
+  </si>
+  <si>
+    <t>dialogue_omakecreature_start_first</t>
+  </si>
+  <si>
+    <t>char_creature</t>
+  </si>
+  <si>
+    <t>이 게임의 장르가 호러라고 생각하시겠지만...
+사실 이 게임은&lt;np&gt;'벌레 괴물과 폐쇄된 연구소에서 알콩달콩 살아가는
+연애 시뮬레이션'입니다.&lt;np&gt;구라입니다.&lt;np&gt;사실 튜토리얼 단계에서 괴물과 상호작용하는
+파트가 있었는데요&lt;np&gt;리소스 뽑기가 힘들어서 후순위로 미뤄지다가
+결국 구현을 못했습니다.&lt;np&gt;그래서 저는 초상화도 없어요ㅠㅠ</t>
+  </si>
+  <si>
+    <t>dialogue_tutopilot_start</t>
+  </si>
+  <si>
+    <t>...연구원님. 국가를 위해 극비 실험에 자원해주셔서
+다시 한 번 진심으로 감사드립니다.</t>
+  </si>
+  <si>
+    <t>dialogue_tutopilot_100</t>
+  </si>
+  <si>
+    <t>이제 마음의 준비는 다 끝나셨나요?</t>
+  </si>
+  <si>
+    <t>준비를 끝냈다, 마음의 준비라니?</t>
+  </si>
+  <si>
+    <t>dialogue_tutopilot_100_selection1, dialogue_tutopilot_100_selection2</t>
+  </si>
+  <si>
+    <t>dialogue_tutopilot_100_selection1</t>
+  </si>
+  <si>
+    <t>지원서에 적힌 대로 침착하시네요. 
+저는 아직도 이곳에만 오면 기분이 나빠지는데 말이죠...&lt;np&gt;그럼 마지막으로 다시 한 번 사건 개요를 설명드리겠습니다.</t>
+  </si>
+  <si>
+    <t>dialogue_tutopilot_110</t>
+  </si>
+  <si>
+    <t>dialogue_tutopilot_100_selection2</t>
+  </si>
+  <si>
+    <t>...긴장도 되지 않으신가 보네요. 정말 대단하십니다.
+저는 아직도 이곳에만 오면 기분이 나빠지는데 말이죠...&lt;np&gt;그럼 마지막으로 다시 한 번 사건 개요를 설명드리겠습니다.</t>
+  </si>
+  <si>
+    <t>#포트폴리오 발표를 해야 하기 때문에 지루하고 현학적인 스토리 설명은 생략하기로 했다.&lt;np&gt;...이상이 연구원님이 이 연구소에 오신 목적입니다.&lt;np&gt;#대화의 자세한 내용은 대화 종료 후 J를 눌러 일지에서 확인할 수 있다.</t>
+  </si>
+  <si>
+    <t>dialogue_tutopilot_120</t>
+  </si>
+  <si>
+    <t>journal_001</t>
+  </si>
+  <si>
+    <t>아, 그러고 보니 아직 카드키를 지급하지 않았네요!&lt;np&gt;이 연구소는 보안 등급이 높아서 카드 키를 입력하지 않으면 출입이 불가능합니다.&lt;np&gt;지금 카드 키를 드릴 테니, 한 번 확인해 보시겠어요?</t>
+  </si>
+  <si>
+    <t>dialogue_tutopilot_130</t>
+  </si>
+  <si>
+    <t>inspectobject_idcard</t>
+  </si>
+  <si>
+    <t>flag_hasidcard</t>
+  </si>
+  <si>
+    <t>dialogue_tutopilot_start_repeat</t>
+  </si>
+  <si>
+    <t>오른쪽으로 가시다 보면 연구소가 보일 겁니다.&lt;np&gt;그럼, 연구원님의 무사를 기원하겠습니다.</t>
+  </si>
+  <si>
+    <t>참고로 받은 물건이나 조사한 것들의 정보는 조사 기록에서 다시 볼 수 있습니다. I키를 눌러서 조사 기록을 열고 확인 가능하니까 나중에 확인해 보세요.&lt;np&gt;이상으로 전달 사항을 모두 마쳤습니다. 오른쪽으로 가시다 보면 연구소가 보일 겁니다.&lt;np&gt;그럼, 연구원님의 무사를 기원하겠습니다.</t>
+  </si>
+  <si>
+    <t>dialogue_tutofirstentercorridor</t>
+  </si>
+  <si>
+    <t>#...이 커다란 섬에 나 혼자라니 뭔가 오싹하네.&lt;np&gt;#아니, 생각해보니 그 괴물도 있었지. 자기가 인간 연구원이라고 착각하고 있는...&lt;np&gt;#생각하니까 더 오싹해졌어...&lt;np&gt;#일단 숙소에 들어가서 짐을 푸는 게 좋겠어.&lt;np&gt;#숙소는 연구소 왼쪽 맨 끝에 있어.</t>
+  </si>
+  <si>
+    <t>flag_endfirstentercorridorevent</t>
+  </si>
+  <si>
+    <t>dialogue_tutofirstentermanquarters</t>
+  </si>
+  <si>
+    <t>#여기가 앞으로 지낼 숙소인가..?&lt;np&gt;#2인 숙소를 혼자 쓰려니까 좀 허전하네.
+일단 좀 둘러봐야겠다.&lt;np&gt;[개발자의 메시지] 숙소를 구석구석 조사해 보세요.&lt;np&gt;방의 중요한 부분들을 모두 조사하면 튜토리얼이 완료됩니다.</t>
+  </si>
+  <si>
+    <t>flag_endfirstentermanquarterevent</t>
+  </si>
+  <si>
+    <t>dialogue_endtutorial_100</t>
+  </si>
+  <si>
+    <t>[개발자의 메시지]축하합니다! 튜토리얼을 모두 완료하셨습니다!&lt;np&gt;아직 게임의 본격적인 스토리는 시작도 안 했고,
+주요 NPC도 한 명도 등장하지 않았지만...&lt;np&gt;개발 시간의 한계 때문에 스토리는 여기에서 끝나게 됩니다.&lt;np&gt;하지만 이후 열릴 특전 모드에서 보지 못한 캐릭터들의 스프라이트와 히로인과의 상호작용을 간단히 체험해 볼 수 있습니다.</t>
+  </si>
+  <si>
+    <t>dialogue_endtutorial_200</t>
+  </si>
+  <si>
+    <t>특전 모드를 개방할까요?</t>
+  </si>
+  <si>
+    <t>네, 좋아요, 그럽시다</t>
+  </si>
+  <si>
+    <t>dialogue_endtutorial_300, dialogue_endtutorial_300, dialogue_endtutorial_300</t>
+  </si>
+  <si>
+    <t>dialogue_endtutorial_300</t>
+  </si>
+  <si>
+    <t>특전 모드로 이동시켜 드리겠습니다.&lt;np&gt;즐겨 주셔서 감사합니다!</t>
+  </si>
+  <si>
+    <t>flag_endtutorial</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -151,6 +322,12 @@
       <color rgb="FF008000"/>
       <name val="Arial"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -191,7 +368,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -214,13 +391,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -253,6 +443,56 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -481,6 +721,9 @@
     <col min="4" max="4" width="51.5703125" customWidth="1"/>
     <col min="5" max="6" width="77.140625" customWidth="1"/>
     <col min="7" max="8" width="50.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" customHeight="1">
@@ -494,6 +737,10 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1">
       <c r="A2" s="8" t="s">
@@ -517,55 +764,79 @@
       <c r="G2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="8"/>
+      <c r="H2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="21"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1">
       <c r="A3" s="14" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="9" t="s">
-        <v>14</v>
-      </c>
+      <c r="G4" s="9"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -575,29 +846,25 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>14</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="15"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -607,25 +874,27 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9" t="s">
-        <v>20</v>
-      </c>
+      <c r="E6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="15"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -635,25 +904,29 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="9"/>
+        <v>26</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>27</v>
+      </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="G7" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="9">
+        <v>10</v>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -663,25 +936,27 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
-      <c r="G8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
+      <c r="G8" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="12">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="26"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -690,18 +965,28 @@
       <c r="R8" s="1"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A9" s="9"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
+      <c r="A9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>33</v>
+      </c>
       <c r="D9" s="12"/>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+      <c r="G9" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="9">
+        <v>-10</v>
+      </c>
+      <c r="I9" s="25"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -711,21 +996,21 @@
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -734,18 +1019,26 @@
       <c r="R10" s="1"/>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="A11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="G11" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="H11" s="4"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -754,18 +1047,24 @@
       <c r="R11" s="1"/>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>41</v>
+      </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -774,18 +1073,24 @@
       <c r="R12" s="1"/>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="A13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -794,18 +1099,24 @@
       <c r="R13" s="1"/>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -822,10 +1133,10 @@
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -834,86 +1145,186 @@
       <c r="R15" s="1"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="A16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A21" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
+      <c r="I21" s="31"/>
+      <c r="J21" t="s">
+        <v>63</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="L21" s="21"/>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>66</v>
+      </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A23" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>67</v>
+      </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I23" s="31"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="21"/>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" customHeight="1">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -922,58 +1333,114 @@
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A25" s="5"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="34"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A25" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
+      <c r="C25" s="20" t="s">
+        <v>69</v>
+      </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A26" s="6"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="L25" s="21"/>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A26" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
+      <c r="C26" s="36" t="s">
+        <v>72</v>
+      </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A27" s="6"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="L26" s="21"/>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A27" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
+      <c r="C27" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A28" s="6"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
+      <c r="C28" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+      <c r="E28" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A29" s="6"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>80</v>
+      </c>
       <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
+      <c r="C29" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I29" s="32"/>
+      <c r="J29" s="34"/>
+      <c r="K29" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="L29" s="21"/>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -982,8 +1449,12 @@
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I30" s="32"/>
+      <c r="J30" s="34"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -992,8 +1463,12 @@
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I31" s="32"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" customHeight="1">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -1002,8 +1477,12 @@
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I32" s="33"/>
+      <c r="J32" s="34"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" customHeight="1">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -1012,8 +1491,12 @@
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I33" s="33"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" customHeight="1">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -1022,8 +1505,12 @@
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I34" s="33"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" customHeight="1">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -1032,20 +1519,24 @@
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:12" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
